--- a/outputs/Block5B_Senate_2026_Race_Stability.xlsx
+++ b/outputs/Block5B_Senate_2026_Race_Stability.xlsx
@@ -58,25 +58,25 @@
     <t>Role</t>
   </si>
   <si>
+    <t>Ohio</t>
+  </si>
+  <si>
     <t>Maine</t>
   </si>
   <si>
+    <t>Texas</t>
+  </si>
+  <si>
     <t>Alaska</t>
   </si>
   <si>
-    <t>Texas</t>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
   </si>
   <si>
     <t>New Hampshire</t>
-  </si>
-  <si>
-    <t>Michigan</t>
-  </si>
-  <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>North Carolina</t>
   </si>
   <si>
     <t>Montana</t>
@@ -507,28 +507,28 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>1.25229017498787</v>
+        <v>3.536611196062931</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
       </c>
       <c r="D2">
-        <v>-1.506144668308227</v>
+        <v>-0.571235076289603</v>
       </c>
       <c r="E2">
-        <v>0.328403642916468</v>
+        <v>1.08373866544242</v>
       </c>
       <c r="F2">
-        <v>4.388637398267414</v>
+        <v>4.652291929545633</v>
       </c>
       <c r="G2">
-        <v>-9.075435312273683</v>
+        <v>-8.394792308505988</v>
       </c>
       <c r="H2">
-        <v>1.750772399588051</v>
+        <v>3.834808259587021</v>
       </c>
       <c r="I2">
-        <v>10.82620771186173</v>
+        <v>12.22960056809301</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -551,34 +551,34 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>1.686016982113115</v>
+        <v>2.324033140639707</v>
       </c>
       <c r="C3" t="s">
         <v>25</v>
       </c>
       <c r="D3">
-        <v>-1.221547391213839</v>
+        <v>-1.907004543598331</v>
       </c>
       <c r="E3">
-        <v>0.6424537334128565</v>
+        <v>-0.04627621553369998</v>
       </c>
       <c r="F3">
-        <v>4.281138390930596</v>
+        <v>4.625858502654114</v>
       </c>
       <c r="G3">
-        <v>-8.655528146621872</v>
+        <v>-9.715725655312269</v>
       </c>
       <c r="H3">
-        <v>1.497081958893681</v>
+        <v>2.275132275132279</v>
       </c>
       <c r="I3">
-        <v>10.15261010551555</v>
+        <v>11.99085793044455</v>
       </c>
       <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
         <v>3</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
       </c>
       <c r="L3">
         <v>60</v>
@@ -595,40 +595,40 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>-0.7843797050406334</v>
+        <v>2.755412717885293</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4">
-        <v>-3.100991117501406</v>
+        <v>-1.455276107381628</v>
       </c>
       <c r="E4">
-        <v>-1.516711512570621</v>
+        <v>0.3743370007903817</v>
       </c>
       <c r="F4">
-        <v>4.864648380335356</v>
+        <v>4.615123897939323</v>
       </c>
       <c r="G4">
-        <v>-11.11754838992667</v>
+        <v>-9.252187445997336</v>
       </c>
       <c r="H4">
-        <v>1.856335754640838</v>
+        <v>2.731370989127548</v>
       </c>
       <c r="I4">
-        <v>12.97388414456751</v>
+        <v>11.98355843512488</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="s">
         <v>27</v>
@@ -639,40 +639,40 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>7.757545040113389</v>
+        <v>3.840986553974431</v>
       </c>
       <c r="C5" t="s">
         <v>25</v>
       </c>
       <c r="D5">
-        <v>5.601396453171871</v>
+        <v>-0.8131438754679923</v>
       </c>
       <c r="E5">
-        <v>7.247328067624592</v>
+        <v>1.162823821636758</v>
       </c>
       <c r="F5">
-        <v>4.635283520068727</v>
+        <v>4.260222881349504</v>
       </c>
       <c r="G5">
-        <v>-2.348561440178459</v>
+        <v>-8.220303607686365</v>
       </c>
       <c r="H5">
-        <v>9.69704849010213</v>
+        <v>1.824833688550286</v>
       </c>
       <c r="I5">
-        <v>12.04560993028059</v>
+        <v>10.04513729623665</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="s">
         <v>27</v>
@@ -683,28 +683,28 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>3.322364192499973</v>
+        <v>4.943406372496832</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
       </c>
       <c r="D6">
-        <v>1.392297270608908</v>
+        <v>0.9993005887098132</v>
       </c>
       <c r="E6">
-        <v>3.203230148048448</v>
+        <v>2.620320855614978</v>
       </c>
       <c r="F6">
-        <v>4.785124955322779</v>
+        <v>4.784032146538402</v>
       </c>
       <c r="G6">
-        <v>-6.995912889582467</v>
+        <v>-7.364608768458694</v>
       </c>
       <c r="H6">
-        <v>5.027582767314211</v>
+        <v>4.695629952630042</v>
       </c>
       <c r="I6">
-        <v>12.02349565689668</v>
+        <v>12.06023872108874</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -716,7 +716,7 @@
         <v>80</v>
       </c>
       <c r="M6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="s">
         <v>27</v>
@@ -727,28 +727,28 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>3.027335204854857</v>
+        <v>9.157892437164534</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
       </c>
       <c r="D7">
-        <v>0.3217350511822473</v>
+        <v>5.209223243648745</v>
       </c>
       <c r="E7">
-        <v>2.032823649239744</v>
+        <v>6.614050023118953</v>
       </c>
       <c r="F7">
-        <v>4.322752131399832</v>
+        <v>4.446910878251219</v>
       </c>
       <c r="G7">
-        <v>-7.176472161128217</v>
+        <v>-2.383298155870026</v>
       </c>
       <c r="H7">
-        <v>3.498315625809795</v>
+        <v>9.334793320558447</v>
       </c>
       <c r="I7">
-        <v>10.67478778693801</v>
+        <v>11.71809147642847</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -771,28 +771,28 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>8.15573551212689</v>
+        <v>7.39330665909661</v>
       </c>
       <c r="C8" t="s">
         <v>25</v>
       </c>
       <c r="D8">
-        <v>5.581654157228656</v>
+        <v>3.831509619698966</v>
       </c>
       <c r="E8">
-        <v>6.943821333383879</v>
+        <v>5.645689870519757</v>
       </c>
       <c r="F8">
-        <v>4.138913238437175</v>
+        <v>4.800491518272278</v>
       </c>
       <c r="G8">
-        <v>-1.695802107663628</v>
+        <v>-4.659479016596833</v>
       </c>
       <c r="H8">
-        <v>8.458498023715421</v>
+        <v>6.872988265807155</v>
       </c>
       <c r="I8">
-        <v>10.15430013137905</v>
+        <v>11.53246728240399</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -804,7 +804,7 @@
         <v>80</v>
       </c>
       <c r="M8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="s">
         <v>27</v>
@@ -815,28 +815,28 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>-28.19535625398524</v>
+        <v>-31.32320758340596</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9">
-        <v>-29.7588816391178</v>
+        <v>-34.21436753287941</v>
       </c>
       <c r="E9">
-        <v>-29.22220350797864</v>
+        <v>-34.44469546991909</v>
       </c>
       <c r="F9">
-        <v>6.40944545551198</v>
+        <v>7.118681133324941</v>
       </c>
       <c r="G9">
-        <v>-39.67221627274333</v>
+        <v>-44.68600897583397</v>
       </c>
       <c r="H9">
-        <v>-21.88581315216757</v>
+        <v>-24.80889506601807</v>
       </c>
       <c r="I9">
-        <v>17.78640312057576</v>
+        <v>19.8771139098159</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -859,28 +859,28 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>-4.13103634630254</v>
+        <v>-2.564161666219964</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
       </c>
       <c r="D10">
-        <v>-6.690922212101691</v>
+        <v>-6.496419300155535</v>
       </c>
       <c r="E10">
-        <v>-4.748170664481129</v>
+        <v>-5.20872947468007</v>
       </c>
       <c r="F10">
-        <v>4.756525853848467</v>
+        <v>5.196810624584419</v>
       </c>
       <c r="G10">
-        <v>-14.69916668017758</v>
+        <v>-14.81185097149338</v>
       </c>
       <c r="H10">
-        <v>-2.410596026490069</v>
+        <v>-0.7921332969134127</v>
       </c>
       <c r="I10">
-        <v>12.28857065368751</v>
+        <v>14.01971767457997</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -903,28 +903,28 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>10.33409373772884</v>
+        <v>12.11951692303765</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
       </c>
       <c r="D11">
-        <v>8.166596743803989</v>
+        <v>7.99084959154156</v>
       </c>
       <c r="E11">
-        <v>9.764152809749833</v>
+        <v>9.736638244105031</v>
       </c>
       <c r="F11">
-        <v>4.588567775436318</v>
+        <v>4.589289931892803</v>
       </c>
       <c r="G11">
-        <v>0.383899469915236</v>
+        <v>0.2041167027681823</v>
       </c>
       <c r="H11">
-        <v>12.31460748976793</v>
+        <v>12.10717929243599</v>
       </c>
       <c r="I11">
-        <v>11.93070801985269</v>
+        <v>11.9030625896678</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -936,7 +936,7 @@
         <v>100</v>
       </c>
       <c r="M11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="s">
         <v>27</v>
@@ -947,28 +947,28 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>-6.011641417509835</v>
+        <v>-1.195522555630652</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
       <c r="D12">
-        <v>-9.155711900886308</v>
+        <v>-5.848245395114906</v>
       </c>
       <c r="E12">
-        <v>-7.215793060150304</v>
+        <v>-3.743365246733134</v>
       </c>
       <c r="F12">
-        <v>4.371509117880124</v>
+        <v>4.433440486832009</v>
       </c>
       <c r="G12">
-        <v>-16.77952132936703</v>
+        <v>-13.52060177460286</v>
       </c>
       <c r="H12">
-        <v>-5.941181113156134</v>
+        <v>-2.976394115430978</v>
       </c>
       <c r="I12">
-        <v>10.83834021621089</v>
+        <v>10.54420765917188</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>100</v>
       </c>
       <c r="M12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="s">
         <v>27</v>

--- a/outputs/Block5B_Senate_2026_Race_Stability.xlsx
+++ b/outputs/Block5B_Senate_2026_Race_Stability.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
   <si>
     <t>STATE</t>
   </si>
@@ -58,37 +58,40 @@
     <t>Role</t>
   </si>
   <si>
+    <t>Maine</t>
+  </si>
+  <si>
     <t>Ohio</t>
   </si>
   <si>
-    <t>Maine</t>
-  </si>
-  <si>
     <t>Texas</t>
   </si>
   <si>
     <t>Alaska</t>
   </si>
   <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
     <t>Michigan</t>
   </si>
   <si>
-    <t>North Carolina</t>
-  </si>
-  <si>
     <t>New Hampshire</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
-    <t>Iowa</t>
-  </si>
-  <si>
-    <t>Georgia</t>
-  </si>
-  <si>
-    <t>Nebraska</t>
   </si>
   <si>
     <t>D</t>
@@ -455,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -507,28 +510,28 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>3.536611196062931</v>
+        <v>0.8469166525530903</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2">
-        <v>-0.571235076289603</v>
+        <v>0.261785597996267</v>
       </c>
       <c r="E2">
-        <v>1.08373866544242</v>
+        <v>0.9486967156734776</v>
       </c>
       <c r="F2">
-        <v>4.652291929545633</v>
+        <v>1.814331707413149</v>
       </c>
       <c r="G2">
-        <v>-8.394792308505988</v>
+        <v>-2.569259812284918</v>
       </c>
       <c r="H2">
-        <v>3.834808259587021</v>
+        <v>1.766411811231215</v>
       </c>
       <c r="I2">
-        <v>12.22960056809301</v>
+        <v>4.335671623516133</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -543,7 +546,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -551,43 +554,43 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2.324033140639707</v>
+        <v>2.002367309587462</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>-1.907004543598331</v>
+        <v>1.550125829543866</v>
       </c>
       <c r="E3">
-        <v>-0.04627621553369998</v>
+        <v>2.207651587783021</v>
       </c>
       <c r="F3">
-        <v>4.625858502654114</v>
+        <v>1.867110101154733</v>
       </c>
       <c r="G3">
-        <v>-9.715725655312269</v>
+        <v>-1.205006012047791</v>
       </c>
       <c r="H3">
-        <v>2.275132275132279</v>
+        <v>3.348513260112512</v>
       </c>
       <c r="I3">
-        <v>11.99085793044455</v>
+        <v>4.553519272160303</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -595,43 +598,43 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>2.755412717885293</v>
+        <v>2.255887754110281</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4">
-        <v>-1.455276107381628</v>
+        <v>1.724738319874471</v>
       </c>
       <c r="E4">
-        <v>0.3743370007903817</v>
+        <v>2.335555605523423</v>
       </c>
       <c r="F4">
-        <v>4.615123897939323</v>
+        <v>1.695999611941588</v>
       </c>
       <c r="G4">
-        <v>-9.252187445997336</v>
+        <v>-0.8853963345259084</v>
       </c>
       <c r="H4">
-        <v>2.731370989127548</v>
+        <v>3.206997084548107</v>
       </c>
       <c r="I4">
-        <v>11.98355843512488</v>
+        <v>4.092393419074015</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -639,43 +642,43 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>3.840986553974431</v>
+        <v>1.823240208781253</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5">
-        <v>-0.8131438754679923</v>
+        <v>1.086765200142358</v>
       </c>
       <c r="E5">
-        <v>1.162823821636758</v>
+        <v>1.650627714162029</v>
       </c>
       <c r="F5">
-        <v>4.260222881349504</v>
+        <v>1.466003638193395</v>
       </c>
       <c r="G5">
-        <v>-8.220303607686365</v>
+        <v>-1.367040994368765</v>
       </c>
       <c r="H5">
-        <v>1.824833688550286</v>
+        <v>2.330258594624844</v>
       </c>
       <c r="I5">
-        <v>10.04513729623665</v>
+        <v>3.69729958899361</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -683,43 +686,43 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>4.943406372496832</v>
+        <v>-51.98769891961852</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>0.9993005887098132</v>
+        <v>-51.32115119118032</v>
       </c>
       <c r="E6">
-        <v>2.620320855614978</v>
+        <v>-53.49871344225288</v>
       </c>
       <c r="F6">
-        <v>4.784032146538402</v>
+        <v>4.404090696348382</v>
       </c>
       <c r="G6">
-        <v>-7.364608768458694</v>
+        <v>-54.7714674968241</v>
       </c>
       <c r="H6">
-        <v>4.695629952630042</v>
+        <v>-44.5744251714401</v>
       </c>
       <c r="I6">
-        <v>12.06023872108874</v>
+        <v>10.197042325384</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -727,43 +730,43 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>9.157892437164534</v>
+        <v>-2.297880558107114</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7">
-        <v>5.209223243648745</v>
+        <v>-2.708224027585973</v>
       </c>
       <c r="E7">
-        <v>6.614050023118953</v>
+        <v>-1.762551866708519</v>
       </c>
       <c r="F7">
-        <v>4.446910878251219</v>
+        <v>2.553569853852589</v>
       </c>
       <c r="G7">
-        <v>-2.383298155870026</v>
+        <v>-6.347373519972038</v>
       </c>
       <c r="H7">
-        <v>9.334793320558447</v>
+        <v>-0.1354646437279925</v>
       </c>
       <c r="I7">
-        <v>11.71809147642847</v>
+        <v>6.211908876244046</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -771,43 +774,43 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>7.39330665909661</v>
+        <v>12.08997314855779</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>3.831509619698966</v>
+        <v>11.15378268474282</v>
       </c>
       <c r="E8">
-        <v>5.645689870519757</v>
+        <v>11.29841758905937</v>
       </c>
       <c r="F8">
-        <v>4.800491518272278</v>
+        <v>1.639156858441609</v>
       </c>
       <c r="G8">
-        <v>-4.659479016596833</v>
+        <v>8.895303070060358</v>
       </c>
       <c r="H8">
-        <v>6.872988265807155</v>
+        <v>13.44452939923259</v>
       </c>
       <c r="I8">
-        <v>11.53246728240399</v>
+        <v>4.54922632917223</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -815,28 +818,28 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>-31.32320758340596</v>
+        <v>-4.163821440088287</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9">
-        <v>-34.21436753287941</v>
+        <v>-4.937332070733922</v>
       </c>
       <c r="E9">
-        <v>-34.44469546991909</v>
+        <v>-4.597516694441605</v>
       </c>
       <c r="F9">
-        <v>7.118681133324941</v>
+        <v>1.550936761335121</v>
       </c>
       <c r="G9">
-        <v>-44.68600897583397</v>
+        <v>-7.512037905258658</v>
       </c>
       <c r="H9">
-        <v>-24.80889506601807</v>
+        <v>-3.5442438966708</v>
       </c>
       <c r="I9">
-        <v>19.8771139098159</v>
+        <v>3.967794008587858</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -851,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -859,28 +862,28 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>-2.564161666219964</v>
+        <v>-2.506725990311326</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10">
-        <v>-6.496419300155535</v>
+        <v>-3.399032573826616</v>
       </c>
       <c r="E10">
-        <v>-5.20872947468007</v>
+        <v>-3.055392597408815</v>
       </c>
       <c r="F10">
-        <v>5.196810624584419</v>
+        <v>1.390844829513239</v>
       </c>
       <c r="G10">
-        <v>-14.81185097149338</v>
+        <v>-5.769932005355074</v>
       </c>
       <c r="H10">
-        <v>-0.7921332969134127</v>
+        <v>-2.086410846675933</v>
       </c>
       <c r="I10">
-        <v>14.01971767457997</v>
+        <v>3.683521158679141</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -895,7 +898,7 @@
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -903,28 +906,28 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>12.11951692303765</v>
+        <v>7.756190899177313</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>7.99084959154156</v>
+        <v>7.417326176799524</v>
       </c>
       <c r="E11">
-        <v>9.736638244105031</v>
+        <v>7.72421770476141</v>
       </c>
       <c r="F11">
-        <v>4.589289931892803</v>
+        <v>1.223275752839552</v>
       </c>
       <c r="G11">
-        <v>0.2041167027681823</v>
+        <v>5.69148527177934</v>
       </c>
       <c r="H11">
-        <v>12.10717929243599</v>
+        <v>8.747300215982712</v>
       </c>
       <c r="I11">
-        <v>11.9030625896678</v>
+        <v>3.055814944203371</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -936,10 +939,10 @@
         <v>100</v>
       </c>
       <c r="M11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -947,43 +950,87 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>-1.195522555630652</v>
+        <v>5.072029400085592</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
       <c r="D12">
-        <v>-5.848245395114906</v>
+        <v>4.240193913443684</v>
       </c>
       <c r="E12">
-        <v>-3.743365246733134</v>
+        <v>4.244061496758697</v>
       </c>
       <c r="F12">
-        <v>4.433440486832009</v>
+        <v>1.135135515353398</v>
       </c>
       <c r="G12">
-        <v>-13.52060177460286</v>
+        <v>2.841236963152701</v>
       </c>
       <c r="H12">
-        <v>-2.976394115430978</v>
+        <v>5.459894800167097</v>
       </c>
       <c r="I12">
-        <v>10.54420765917188</v>
+        <v>2.618657837014397</v>
       </c>
       <c r="J12">
+        <v>5</v>
+      </c>
+      <c r="K12">
         <v>0</v>
-      </c>
-      <c r="K12">
-        <v>5</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13">
+        <v>8.678124461072677</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <v>7.986099807306672</v>
+      </c>
+      <c r="E13">
+        <v>7.795829409818411</v>
+      </c>
+      <c r="F13">
+        <v>0.9296914008026093</v>
+      </c>
+      <c r="G13">
+        <v>7.102040816326536</v>
+      </c>
+      <c r="H13">
+        <v>9.183589830365031</v>
+      </c>
+      <c r="I13">
+        <v>2.081549014038496</v>
+      </c>
+      <c r="J13">
+        <v>5</v>
+      </c>
+      <c r="K13">
         <v>0</v>
       </c>
-      <c r="N12" t="s">
-        <v>27</v>
+      <c r="L13">
+        <v>100</v>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5B_Senate_2026_Race_Stability.xlsx
+++ b/outputs/Block5B_Senate_2026_Race_Stability.xlsx
@@ -61,28 +61,28 @@
     <t>Maine</t>
   </si>
   <si>
+    <t>Iowa</t>
+  </si>
+  <si>
     <t>Ohio</t>
   </si>
   <si>
     <t>Texas</t>
   </si>
   <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
     <t>Alaska</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
-    <t>Iowa</t>
-  </si>
-  <si>
-    <t>Georgia</t>
-  </si>
-  <si>
-    <t>Kansas</t>
-  </si>
-  <si>
-    <t>Nebraska</t>
   </si>
   <si>
     <t>North Carolina</t>
@@ -510,28 +510,28 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.8469166525530903</v>
+        <v>1.025282361097076</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2">
-        <v>0.261785597996267</v>
+        <v>0.3212397038682321</v>
       </c>
       <c r="E2">
-        <v>0.9486967156734776</v>
+        <v>0.9514087679052214</v>
       </c>
       <c r="F2">
-        <v>1.814331707413149</v>
+        <v>1.613698999309472</v>
       </c>
       <c r="G2">
-        <v>-2.569259812284918</v>
+        <v>-2.330206567847096</v>
       </c>
       <c r="H2">
-        <v>1.766411811231215</v>
+        <v>1.644285686526526</v>
       </c>
       <c r="I2">
-        <v>4.335671623516133</v>
+        <v>3.974492254373622</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -554,34 +554,34 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2.002367309587462</v>
+        <v>-1.081257860747497</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3">
-        <v>1.550125829543866</v>
+        <v>-1.581635835849838</v>
       </c>
       <c r="E3">
-        <v>2.207651587783021</v>
+        <v>-0.7317537907371487</v>
       </c>
       <c r="F3">
-        <v>1.867110101154733</v>
+        <v>2.234689236461155</v>
       </c>
       <c r="G3">
-        <v>-1.205006012047791</v>
+        <v>-4.901089640803971</v>
       </c>
       <c r="H3">
-        <v>3.348513260112512</v>
+        <v>0.507614213197968</v>
       </c>
       <c r="I3">
-        <v>4.553519272160303</v>
+        <v>5.408703854001939</v>
       </c>
       <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
         <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
       </c>
       <c r="L3">
         <v>80</v>
@@ -598,28 +598,28 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>2.255887754110281</v>
+        <v>2.517951045482532</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
       </c>
       <c r="D4">
-        <v>1.724738319874471</v>
+        <v>2.220331063562673</v>
       </c>
       <c r="E4">
-        <v>2.335555605523423</v>
+        <v>2.899996931338003</v>
       </c>
       <c r="F4">
-        <v>1.695999611941588</v>
+        <v>2.074011747791157</v>
       </c>
       <c r="G4">
-        <v>-0.8853963345259084</v>
+        <v>-0.6118390830274762</v>
       </c>
       <c r="H4">
-        <v>3.206997084548107</v>
+        <v>4.480874316939889</v>
       </c>
       <c r="I4">
-        <v>4.092393419074015</v>
+        <v>5.092713399967366</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -642,28 +642,28 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>1.823240208781253</v>
+        <v>1.890281525642506</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
       </c>
       <c r="D5">
-        <v>1.086765200142358</v>
+        <v>1.320446152533756</v>
       </c>
       <c r="E5">
-        <v>1.650627714162029</v>
+        <v>1.941552954463196</v>
       </c>
       <c r="F5">
-        <v>1.466003638193395</v>
+        <v>1.684552269206111</v>
       </c>
       <c r="G5">
-        <v>-1.367040994368765</v>
+        <v>-1.315406838751676</v>
       </c>
       <c r="H5">
-        <v>2.330258594624844</v>
+        <v>2.716961223951465</v>
       </c>
       <c r="I5">
-        <v>3.69729958899361</v>
+        <v>4.03236806270314</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -686,28 +686,28 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>-51.98769891961852</v>
+        <v>-52.43341001920999</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6">
-        <v>-51.32115119118032</v>
+        <v>-51.81038392245694</v>
       </c>
       <c r="E6">
-        <v>-53.49871344225288</v>
+        <v>-54.08145851217775</v>
       </c>
       <c r="F6">
-        <v>4.404090696348382</v>
+        <v>4.27063725910124</v>
       </c>
       <c r="G6">
-        <v>-54.7714674968241</v>
+        <v>-55.07160583275694</v>
       </c>
       <c r="H6">
-        <v>-44.5744251714401</v>
+        <v>-45.26484751203853</v>
       </c>
       <c r="I6">
-        <v>10.197042325384</v>
+        <v>9.806758320718416</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -730,34 +730,34 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>-2.297880558107114</v>
+        <v>12.14710898697921</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>-2.708224027585973</v>
+        <v>11.21281940904447</v>
       </c>
       <c r="E7">
-        <v>-1.762551866708519</v>
+        <v>11.36905065506951</v>
       </c>
       <c r="F7">
-        <v>2.553569853852589</v>
+        <v>1.643393812986157</v>
       </c>
       <c r="G7">
-        <v>-6.347373519972038</v>
+        <v>8.947782734190504</v>
       </c>
       <c r="H7">
-        <v>-0.1354646437279925</v>
+        <v>13.50866379811078</v>
       </c>
       <c r="I7">
-        <v>6.211908876244046</v>
+        <v>4.560881063920277</v>
       </c>
       <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
         <v>0</v>
-      </c>
-      <c r="K7">
-        <v>5</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -774,34 +774,34 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>12.08997314855779</v>
+        <v>-3.902688230755659</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8">
-        <v>11.15378268474282</v>
+        <v>-4.665891981871175</v>
       </c>
       <c r="E8">
-        <v>11.29841758905937</v>
+        <v>-4.291456125233902</v>
       </c>
       <c r="F8">
-        <v>1.639156858441609</v>
+        <v>1.578746721333865</v>
       </c>
       <c r="G8">
-        <v>8.895303070060358</v>
+        <v>-7.280315694596965</v>
       </c>
       <c r="H8">
-        <v>13.44452939923259</v>
+        <v>-3.265242901320678</v>
       </c>
       <c r="I8">
-        <v>4.54922632917223</v>
+        <v>4.015072793276287</v>
       </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>5</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -818,28 +818,28 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>-4.163821440088287</v>
+        <v>-4.226188759552537</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9">
-        <v>-4.937332070733922</v>
+        <v>-5.175726474986953</v>
       </c>
       <c r="E9">
-        <v>-4.597516694441605</v>
+        <v>-4.993160057968772</v>
       </c>
       <c r="F9">
-        <v>1.550936761335121</v>
+        <v>1.261868013546693</v>
       </c>
       <c r="G9">
-        <v>-7.512037905258658</v>
+        <v>-7.284368204258474</v>
       </c>
       <c r="H9">
-        <v>-3.5442438966708</v>
+        <v>-3.923234843247019</v>
       </c>
       <c r="I9">
-        <v>3.967794008587858</v>
+        <v>3.361133361011455</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -862,34 +862,34 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>-2.506725990311326</v>
+        <v>3.113148128678475</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>-3.399032573826616</v>
+        <v>2.227623337357799</v>
       </c>
       <c r="E10">
-        <v>-3.055392597408815</v>
+        <v>2.6354708915347</v>
       </c>
       <c r="F10">
-        <v>1.390844829513239</v>
+        <v>1.181665279921507</v>
       </c>
       <c r="G10">
-        <v>-5.769932005355074</v>
+        <v>0.2140625270838568</v>
       </c>
       <c r="H10">
-        <v>-2.086410846675933</v>
+        <v>3.313029187313943</v>
       </c>
       <c r="I10">
-        <v>3.683521158679141</v>
+        <v>3.098966660230086</v>
       </c>
       <c r="J10">
+        <v>5</v>
+      </c>
+      <c r="K10">
         <v>0</v>
-      </c>
-      <c r="K10">
-        <v>5</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -906,28 +906,28 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>7.756190899177313</v>
+        <v>8.97833754582547</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11">
-        <v>7.417326176799524</v>
+        <v>8.6910148699688</v>
       </c>
       <c r="E11">
-        <v>7.72421770476141</v>
+        <v>8.933398731517775</v>
       </c>
       <c r="F11">
-        <v>1.223275752839552</v>
+        <v>1.138703198141632</v>
       </c>
       <c r="G11">
-        <v>5.69148527177934</v>
+        <v>7.153485216836731</v>
       </c>
       <c r="H11">
-        <v>8.747300215982712</v>
+        <v>10.0135685210312</v>
       </c>
       <c r="I11">
-        <v>3.055814944203371</v>
+        <v>2.860083304194473</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -950,28 +950,28 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>5.072029400085592</v>
+        <v>5.86081668083678</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
       <c r="D12">
-        <v>4.240193913443684</v>
+        <v>4.962595093015557</v>
       </c>
       <c r="E12">
-        <v>4.244061496758697</v>
+        <v>4.887609653950286</v>
       </c>
       <c r="F12">
-        <v>1.135135515353398</v>
+        <v>1.211729673289186</v>
       </c>
       <c r="G12">
-        <v>2.841236963152701</v>
+        <v>3.772582359192349</v>
       </c>
       <c r="H12">
-        <v>5.459894800167097</v>
+        <v>6.46897996696539</v>
       </c>
       <c r="I12">
-        <v>2.618657837014397</v>
+        <v>2.696397607773042</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -994,28 +994,28 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>8.678124461072677</v>
+        <v>9.126009195964262</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
       </c>
       <c r="D13">
-        <v>7.986099807306672</v>
+        <v>8.441614472091578</v>
       </c>
       <c r="E13">
-        <v>7.795829409818411</v>
+        <v>8.223343481368309</v>
       </c>
       <c r="F13">
-        <v>0.9296914008026093</v>
+        <v>0.9267049194147077</v>
       </c>
       <c r="G13">
-        <v>7.102040816326536</v>
+        <v>7.512248230811103</v>
       </c>
       <c r="H13">
-        <v>9.183589830365031</v>
+        <v>9.66968012404757</v>
       </c>
       <c r="I13">
-        <v>2.081549014038496</v>
+        <v>2.157431893236467</v>
       </c>
       <c r="J13">
         <v>5</v>

--- a/outputs/Block5B_Senate_2026_Race_Stability.xlsx
+++ b/outputs/Block5B_Senate_2026_Race_Stability.xlsx
@@ -58,46 +58,46 @@
     <t>Role</t>
   </si>
   <si>
+    <t>Iowa</t>
+  </si>
+  <si>
     <t>Maine</t>
   </si>
   <si>
-    <t>Iowa</t>
-  </si>
-  <si>
     <t>Ohio</t>
   </si>
   <si>
     <t>Texas</t>
   </si>
   <si>
+    <t>Alaska</t>
+  </si>
+  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Kansas</t>
+  </si>
+  <si>
     <t>Georgia</t>
   </si>
   <si>
-    <t>Kansas</t>
-  </si>
-  <si>
     <t>Nebraska</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
     <t>North Carolina</t>
   </si>
   <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
     <t>Michigan</t>
   </si>
   <si>
-    <t>New Hampshire</t>
+    <t>R</t>
   </si>
   <si>
     <t>D</t>
-  </si>
-  <si>
-    <t>R</t>
   </si>
   <si>
     <t>Sensitivity diagnostic; never a Senate seat quota</t>
@@ -510,34 +510,34 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>1.025282361097076</v>
+        <v>-0.989792013058824</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2">
-        <v>0.3212397038682321</v>
+        <v>-1.478084452513821</v>
       </c>
       <c r="E2">
-        <v>0.9514087679052214</v>
+        <v>-0.6344447829808589</v>
       </c>
       <c r="F2">
-        <v>1.613698999309472</v>
+        <v>2.192411832093762</v>
       </c>
       <c r="G2">
-        <v>-2.330206567847096</v>
+        <v>-4.753870159985402</v>
       </c>
       <c r="H2">
-        <v>1.644285686526526</v>
+        <v>0.5601493731661762</v>
       </c>
       <c r="I2">
-        <v>3.974492254373622</v>
+        <v>5.314019533151578</v>
       </c>
       <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
         <v>3</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
       </c>
       <c r="L2">
         <v>60</v>
@@ -554,37 +554,37 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>-1.081257860747497</v>
+        <v>0.9966628240956751</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
       </c>
       <c r="D3">
-        <v>-1.581635835849838</v>
+        <v>0.3096676887812282</v>
       </c>
       <c r="E3">
-        <v>-0.7317537907371487</v>
+        <v>0.9436425056113893</v>
       </c>
       <c r="F3">
-        <v>2.234689236461155</v>
+        <v>1.599398649494657</v>
       </c>
       <c r="G3">
-        <v>-4.901089640803971</v>
+        <v>-2.328295474778286</v>
       </c>
       <c r="H3">
-        <v>0.507614213197968</v>
+        <v>1.6066362667385</v>
       </c>
       <c r="I3">
-        <v>5.408703854001939</v>
+        <v>3.934931741516786</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
@@ -598,28 +598,28 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>2.517951045482532</v>
+        <v>2.528247976997612</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4">
-        <v>2.220331063562673</v>
+        <v>2.252108967062852</v>
       </c>
       <c r="E4">
-        <v>2.899996931338003</v>
+        <v>2.934575079507524</v>
       </c>
       <c r="F4">
-        <v>2.074011747791157</v>
+        <v>2.060221306212681</v>
       </c>
       <c r="G4">
-        <v>-0.6118390830274762</v>
+        <v>-0.5639709206460912</v>
       </c>
       <c r="H4">
-        <v>4.480874316939889</v>
+        <v>4.506965310024583</v>
       </c>
       <c r="I4">
-        <v>5.092713399967366</v>
+        <v>5.070936230670674</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -642,28 +642,28 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>1.890281525642506</v>
+        <v>2.151942732195052</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5">
-        <v>1.320446152533756</v>
+        <v>1.583606971907368</v>
       </c>
       <c r="E5">
-        <v>1.941552954463196</v>
+        <v>2.182906480618617</v>
       </c>
       <c r="F5">
-        <v>1.684552269206111</v>
+        <v>1.603413826435776</v>
       </c>
       <c r="G5">
-        <v>-1.315406838751676</v>
+        <v>-0.9615771044751797</v>
       </c>
       <c r="H5">
-        <v>2.716961223951465</v>
+        <v>2.866158296082041</v>
       </c>
       <c r="I5">
-        <v>4.03236806270314</v>
+        <v>3.827735400557221</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -686,37 +686,37 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>-52.43341001920999</v>
+        <v>2.567902670573524</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6">
-        <v>-51.81038392245694</v>
+        <v>1.907967009786827</v>
       </c>
       <c r="E6">
-        <v>-54.08145851217775</v>
+        <v>2.444738081797682</v>
       </c>
       <c r="F6">
-        <v>4.27063725910124</v>
+        <v>1.416781622662683</v>
       </c>
       <c r="G6">
-        <v>-55.07160583275694</v>
+        <v>-0.4442868396550299</v>
       </c>
       <c r="H6">
-        <v>-45.26484751203853</v>
+        <v>3.067539176143721</v>
       </c>
       <c r="I6">
-        <v>9.806758320718416</v>
+        <v>3.511826015798751</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -730,34 +730,34 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>12.14710898697921</v>
+        <v>-52.47074353204474</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7">
-        <v>11.21281940904447</v>
+        <v>-51.82713990785758</v>
       </c>
       <c r="E7">
-        <v>11.36905065506951</v>
+        <v>-54.09591616858408</v>
       </c>
       <c r="F7">
-        <v>1.643393812986157</v>
+        <v>4.259543670345415</v>
       </c>
       <c r="G7">
-        <v>8.947782734190504</v>
+        <v>-55.07222437890977</v>
       </c>
       <c r="H7">
-        <v>13.50866379811078</v>
+        <v>-45.28680304853589</v>
       </c>
       <c r="I7">
-        <v>4.560881063920277</v>
+        <v>9.785421330373872</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>5</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -774,28 +774,28 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>-3.902688230755659</v>
+        <v>-2.96367748428117</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>-4.665891981871175</v>
+        <v>-3.439781783386437</v>
       </c>
       <c r="E8">
-        <v>-4.291456125233902</v>
+        <v>-2.653435444606227</v>
       </c>
       <c r="F8">
-        <v>1.578746721333865</v>
+        <v>2.268524276074299</v>
       </c>
       <c r="G8">
-        <v>-7.280315694596965</v>
+        <v>-6.797050512559895</v>
       </c>
       <c r="H8">
-        <v>-3.265242901320678</v>
+        <v>-1.263101316850296</v>
       </c>
       <c r="I8">
-        <v>4.015072793276287</v>
+        <v>5.533949195709599</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -818,34 +818,34 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>-4.226188759552537</v>
+        <v>12.80573215770047</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9">
-        <v>-5.175726474986953</v>
+        <v>11.81165239927035</v>
       </c>
       <c r="E9">
-        <v>-4.993160057968772</v>
+        <v>12.03363747660556</v>
       </c>
       <c r="F9">
-        <v>1.261868013546693</v>
+        <v>1.902614896966285</v>
       </c>
       <c r="G9">
-        <v>-7.284368204258474</v>
+        <v>9.156939040207519</v>
       </c>
       <c r="H9">
-        <v>-3.923234843247019</v>
+        <v>14.43379052856994</v>
       </c>
       <c r="I9">
-        <v>3.361133361011455</v>
+        <v>5.276851488362418</v>
       </c>
       <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9">
         <v>0</v>
-      </c>
-      <c r="K9">
-        <v>5</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -862,34 +862,34 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>3.113148128678475</v>
+        <v>-4.646765651724422</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
       </c>
       <c r="D10">
-        <v>2.227623337357799</v>
+        <v>-5.57126411371098</v>
       </c>
       <c r="E10">
-        <v>2.6354708915347</v>
+        <v>-5.37855430626928</v>
       </c>
       <c r="F10">
-        <v>1.181665279921507</v>
+        <v>1.246184226949998</v>
       </c>
       <c r="G10">
-        <v>0.2140625270838568</v>
+        <v>-7.65381576757183</v>
       </c>
       <c r="H10">
-        <v>3.313029187313943</v>
+        <v>-4.344700706520976</v>
       </c>
       <c r="I10">
-        <v>3.098966660230086</v>
+        <v>3.309115061050854</v>
       </c>
       <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>5</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -906,28 +906,28 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>8.97833754582547</v>
+        <v>9.131621293041764</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11">
-        <v>8.6910148699688</v>
+        <v>8.86916486441446</v>
       </c>
       <c r="E11">
-        <v>8.933398731517775</v>
+        <v>9.105846979584094</v>
       </c>
       <c r="F11">
-        <v>1.138703198141632</v>
+        <v>1.110633499156545</v>
       </c>
       <c r="G11">
-        <v>7.153485216836731</v>
+        <v>7.372629814854099</v>
       </c>
       <c r="H11">
-        <v>10.0135685210312</v>
+        <v>10.17639077340569</v>
       </c>
       <c r="I11">
-        <v>2.860083304194473</v>
+        <v>2.803760958551594</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -950,28 +950,28 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>5.86081668083678</v>
+        <v>9.044684952983104</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>4.962595093015557</v>
+        <v>8.289435017027877</v>
       </c>
       <c r="E12">
-        <v>4.887609653950286</v>
+        <v>8.045819412749589</v>
       </c>
       <c r="F12">
-        <v>1.211729673289186</v>
+        <v>1.083125693979511</v>
       </c>
       <c r="G12">
-        <v>3.772582359192349</v>
+        <v>7.043010752688183</v>
       </c>
       <c r="H12">
-        <v>6.46897996696539</v>
+        <v>9.796187483455562</v>
       </c>
       <c r="I12">
-        <v>2.696397607773042</v>
+        <v>2.753176730767379</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -994,28 +994,28 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>9.126009195964262</v>
+        <v>5.861701259318181</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13">
-        <v>8.441614472091578</v>
+        <v>5.013328773407792</v>
       </c>
       <c r="E13">
-        <v>8.223343481368309</v>
+        <v>4.952355098335075</v>
       </c>
       <c r="F13">
-        <v>0.9267049194147077</v>
+        <v>1.167921684144027</v>
       </c>
       <c r="G13">
-        <v>7.512248230811103</v>
+        <v>3.835568370743952</v>
       </c>
       <c r="H13">
-        <v>9.66968012404757</v>
+        <v>6.450046158743803</v>
       </c>
       <c r="I13">
-        <v>2.157431893236467</v>
+        <v>2.614477787999852</v>
       </c>
       <c r="J13">
         <v>5</v>

--- a/outputs/Block5B_Senate_2026_Race_Stability.xlsx
+++ b/outputs/Block5B_Senate_2026_Race_Stability.xlsx
@@ -58,27 +58,27 @@
     <t>Role</t>
   </si>
   <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
     <t>Iowa</t>
   </si>
   <si>
-    <t>Maine</t>
-  </si>
-  <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
-    <t>Kansas</t>
-  </si>
-  <si>
     <t>Georgia</t>
   </si>
   <si>
@@ -88,10 +88,10 @@
     <t>North Carolina</t>
   </si>
   <si>
+    <t>Michigan</t>
+  </si>
+  <si>
     <t>New Hampshire</t>
-  </si>
-  <si>
-    <t>Michigan</t>
   </si>
   <si>
     <t>R</t>
@@ -510,37 +510,37 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>-0.989792013058824</v>
+        <v>-1.668982094438827</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2">
-        <v>-1.478084452513821</v>
+        <v>-2.082159330100257</v>
       </c>
       <c r="E2">
-        <v>-0.6344447829808589</v>
+        <v>-1.153267653173353</v>
       </c>
       <c r="F2">
-        <v>2.192411832093762</v>
+        <v>2.551679662651943</v>
       </c>
       <c r="G2">
-        <v>-4.753870159985402</v>
+        <v>-5.680203385192162</v>
       </c>
       <c r="H2">
-        <v>0.5601493731661762</v>
+        <v>0.5161640858462349</v>
       </c>
       <c r="I2">
-        <v>5.314019533151578</v>
+        <v>6.196367471038397</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -554,37 +554,37 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.9966628240956751</v>
+        <v>2.361497500491866</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
       </c>
       <c r="D3">
-        <v>0.3096676887812282</v>
+        <v>2.039296644553422</v>
       </c>
       <c r="E3">
-        <v>0.9436425056113893</v>
+        <v>2.726879376671175</v>
       </c>
       <c r="F3">
-        <v>1.599398649494657</v>
+        <v>2.126226822090575</v>
       </c>
       <c r="G3">
-        <v>-2.328295474778286</v>
+        <v>-0.8514681264693413</v>
       </c>
       <c r="H3">
-        <v>1.6066362667385</v>
+        <v>4.35020519835841</v>
       </c>
       <c r="I3">
-        <v>3.934931741516786</v>
+        <v>5.201673324827751</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
@@ -598,28 +598,28 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>2.528247976997612</v>
+        <v>1.615349717881234</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4">
-        <v>2.252108967062852</v>
+        <v>1.001518801299071</v>
       </c>
       <c r="E4">
-        <v>2.934575079507524</v>
+        <v>1.631399086505698</v>
       </c>
       <c r="F4">
-        <v>2.060221306212681</v>
+        <v>1.721319065125029</v>
       </c>
       <c r="G4">
-        <v>-0.5639709206460912</v>
+        <v>-1.693838513232154</v>
       </c>
       <c r="H4">
-        <v>4.506965310024583</v>
+        <v>2.397891963109359</v>
       </c>
       <c r="I4">
-        <v>5.070936230670674</v>
+        <v>4.091730476341513</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -642,28 +642,28 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>2.151942732195052</v>
+        <v>1.784559241874853</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
       </c>
       <c r="D5">
-        <v>1.583606971907368</v>
+        <v>1.05646767722283</v>
       </c>
       <c r="E5">
-        <v>2.182906480618617</v>
+        <v>1.63222527052263</v>
       </c>
       <c r="F5">
-        <v>1.603413826435776</v>
+        <v>1.534599067282088</v>
       </c>
       <c r="G5">
-        <v>-0.9615771044751797</v>
+        <v>-1.468962141794489</v>
       </c>
       <c r="H5">
-        <v>2.866158296082041</v>
+        <v>2.350626952871099</v>
       </c>
       <c r="I5">
-        <v>3.827735400557221</v>
+        <v>3.819589094665589</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -686,28 +686,28 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>2.567902670573524</v>
+        <v>2.056327975391802</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6">
-        <v>1.907967009786827</v>
+        <v>1.33487258636382</v>
       </c>
       <c r="E6">
-        <v>2.444738081797682</v>
+        <v>1.894546052252768</v>
       </c>
       <c r="F6">
-        <v>1.416781622662683</v>
+        <v>1.505530763105608</v>
       </c>
       <c r="G6">
-        <v>-0.4442868396550299</v>
+        <v>-1.143462461900912</v>
       </c>
       <c r="H6">
-        <v>3.067539176143721</v>
+        <v>2.605762487767027</v>
       </c>
       <c r="I6">
-        <v>3.511826015798751</v>
+        <v>3.749224949667938</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -730,28 +730,28 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>-52.47074353204474</v>
+        <v>-53.87625990793708</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7">
-        <v>-51.82713990785758</v>
+        <v>-53.23840110665137</v>
       </c>
       <c r="E7">
-        <v>-54.09591616858408</v>
+        <v>-55.59266721589984</v>
       </c>
       <c r="F7">
-        <v>4.259543670345415</v>
+        <v>4.390514382090063</v>
       </c>
       <c r="G7">
-        <v>-55.07222437890977</v>
+        <v>-56.62306739616567</v>
       </c>
       <c r="H7">
-        <v>-45.28680304853589</v>
+        <v>-46.50877909350755</v>
       </c>
       <c r="I7">
-        <v>9.785421330373872</v>
+        <v>10.11428830265812</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -774,28 +774,28 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>-2.96367748428117</v>
+        <v>-2.500784269168561</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8">
-        <v>-3.439781783386437</v>
+        <v>-2.962365486903869</v>
       </c>
       <c r="E8">
-        <v>-2.653435444606227</v>
+        <v>-2.070518893146442</v>
       </c>
       <c r="F8">
-        <v>2.268524276074299</v>
+        <v>2.494497553471604</v>
       </c>
       <c r="G8">
-        <v>-6.797050512559895</v>
+        <v>-6.543068817687839</v>
       </c>
       <c r="H8">
-        <v>-1.263101316850296</v>
+        <v>-0.4870129870129816</v>
       </c>
       <c r="I8">
-        <v>5.533949195709599</v>
+        <v>6.056055830674858</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -818,19 +818,19 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>12.80573215770047</v>
+        <v>12.876553924134</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9">
-        <v>11.81165239927035</v>
+        <v>11.82646376574064</v>
       </c>
       <c r="E9">
-        <v>12.03363747660556</v>
+        <v>12.107694308957</v>
       </c>
       <c r="F9">
-        <v>1.902614896966285</v>
+        <v>1.905061701066394</v>
       </c>
       <c r="G9">
         <v>9.156939040207519</v>
@@ -862,28 +862,28 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>-4.646765651724422</v>
+        <v>-3.399779170644565</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
       </c>
       <c r="D10">
-        <v>-5.57126411371098</v>
+        <v>-4.111525374436573</v>
       </c>
       <c r="E10">
-        <v>-5.37855430626928</v>
+        <v>-3.602599519005729</v>
       </c>
       <c r="F10">
-        <v>1.246184226949998</v>
+        <v>1.796311822910402</v>
       </c>
       <c r="G10">
-        <v>-7.65381576757183</v>
+        <v>-6.983595800042814</v>
       </c>
       <c r="H10">
-        <v>-4.344700706520976</v>
+        <v>-2.606691039635062</v>
       </c>
       <c r="I10">
-        <v>3.309115061050854</v>
+        <v>4.376904760407752</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -906,28 +906,28 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>9.131621293041764</v>
+        <v>9.543498182490687</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
       </c>
       <c r="D11">
-        <v>8.86916486441446</v>
+        <v>9.279074024359335</v>
       </c>
       <c r="E11">
-        <v>9.105846979584094</v>
+        <v>9.497791515143108</v>
       </c>
       <c r="F11">
-        <v>1.110633499156545</v>
+        <v>1.179549604622028</v>
       </c>
       <c r="G11">
-        <v>7.372629814854099</v>
+        <v>7.772537436199933</v>
       </c>
       <c r="H11">
-        <v>10.17639077340569</v>
+        <v>10.7103825136612</v>
       </c>
       <c r="I11">
-        <v>2.803760958551594</v>
+        <v>2.937845077461269</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -950,28 +950,28 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>9.044684952983104</v>
+        <v>4.803504661876866</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
       </c>
       <c r="D12">
-        <v>8.289435017027877</v>
+        <v>3.912833396743513</v>
       </c>
       <c r="E12">
-        <v>8.045819412749589</v>
+        <v>3.919246691079949</v>
       </c>
       <c r="F12">
-        <v>1.083125693979511</v>
+        <v>1.180333129680543</v>
       </c>
       <c r="G12">
-        <v>7.043010752688183</v>
+        <v>2.475588634409105</v>
       </c>
       <c r="H12">
-        <v>9.796187483455562</v>
+        <v>5.171540530193047</v>
       </c>
       <c r="I12">
-        <v>2.753176730767379</v>
+        <v>2.695951895783942</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -994,28 +994,28 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>5.861701259318181</v>
+        <v>9.138347262535573</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
       </c>
       <c r="D13">
-        <v>5.013328773407792</v>
+        <v>8.351694851278971</v>
       </c>
       <c r="E13">
-        <v>4.952355098335075</v>
+        <v>8.100876252980063</v>
       </c>
       <c r="F13">
-        <v>1.167921684144027</v>
+        <v>1.050821149840632</v>
       </c>
       <c r="G13">
-        <v>3.835568370743952</v>
+        <v>7.173678532901825</v>
       </c>
       <c r="H13">
-        <v>6.450046158743803</v>
+        <v>9.773277512312969</v>
       </c>
       <c r="I13">
-        <v>2.614477787999852</v>
+        <v>2.599598979411144</v>
       </c>
       <c r="J13">
         <v>5</v>

--- a/outputs/Block5B_Senate_2026_Race_Stability.xlsx
+++ b/outputs/Block5B_Senate_2026_Race_Stability.xlsx
@@ -61,6 +61,9 @@
     <t>Kansas</t>
   </si>
   <si>
+    <t>Iowa</t>
+  </si>
+  <si>
     <t>Ohio</t>
   </si>
   <si>
@@ -76,13 +79,10 @@
     <t>Montana</t>
   </si>
   <si>
-    <t>Iowa</t>
+    <t>Nebraska</t>
   </si>
   <si>
     <t>Georgia</t>
-  </si>
-  <si>
-    <t>Nebraska</t>
   </si>
   <si>
     <t>North Carolina</t>
@@ -554,34 +554,34 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2.361497500491866</v>
+        <v>-1.992304939694847</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>2.039296644553422</v>
+        <v>-2.434965244096224</v>
       </c>
       <c r="E3">
-        <v>2.726879376671175</v>
+        <v>-1.494981145138496</v>
       </c>
       <c r="F3">
-        <v>2.126226822090575</v>
+        <v>2.545132579532559</v>
       </c>
       <c r="G3">
-        <v>-0.8514681264693413</v>
+        <v>-6.063399526031018</v>
       </c>
       <c r="H3">
-        <v>4.35020519835841</v>
+        <v>0.1082837033026536</v>
       </c>
       <c r="I3">
-        <v>5.201673324827751</v>
+        <v>6.171683229333672</v>
       </c>
       <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
         <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
       </c>
       <c r="L3">
         <v>80</v>
@@ -598,28 +598,28 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>1.615349717881234</v>
+        <v>2.361497500491866</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4">
-        <v>1.001518801299071</v>
+        <v>2.039296644553422</v>
       </c>
       <c r="E4">
-        <v>1.631399086505698</v>
+        <v>2.726879376671175</v>
       </c>
       <c r="F4">
-        <v>1.721319065125029</v>
+        <v>2.126226822090575</v>
       </c>
       <c r="G4">
-        <v>-1.693838513232154</v>
+        <v>-0.8514681264693413</v>
       </c>
       <c r="H4">
-        <v>2.397891963109359</v>
+        <v>4.35020519835841</v>
       </c>
       <c r="I4">
-        <v>4.091730476341513</v>
+        <v>5.201673324827751</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -642,28 +642,28 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>1.784559241874853</v>
+        <v>1.615349717881234</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
       </c>
       <c r="D5">
-        <v>1.05646767722283</v>
+        <v>1.001518801299071</v>
       </c>
       <c r="E5">
-        <v>1.63222527052263</v>
+        <v>1.631399086505698</v>
       </c>
       <c r="F5">
-        <v>1.534599067282088</v>
+        <v>1.721319065125029</v>
       </c>
       <c r="G5">
-        <v>-1.468962141794489</v>
+        <v>-1.693838513232154</v>
       </c>
       <c r="H5">
-        <v>2.350626952871099</v>
+        <v>2.397891963109359</v>
       </c>
       <c r="I5">
-        <v>3.819589094665589</v>
+        <v>4.091730476341513</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -686,28 +686,28 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>2.056327975391802</v>
+        <v>1.784559241874853</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6">
-        <v>1.33487258636382</v>
+        <v>1.05646767722283</v>
       </c>
       <c r="E6">
-        <v>1.894546052252768</v>
+        <v>1.63222527052263</v>
       </c>
       <c r="F6">
-        <v>1.505530763105608</v>
+        <v>1.534599067282088</v>
       </c>
       <c r="G6">
-        <v>-1.143462461900912</v>
+        <v>-1.468962141794489</v>
       </c>
       <c r="H6">
-        <v>2.605762487767027</v>
+        <v>2.350626952871099</v>
       </c>
       <c r="I6">
-        <v>3.749224949667938</v>
+        <v>3.819589094665589</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -730,37 +730,37 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>-53.87625990793708</v>
+        <v>2.056327975391802</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7">
-        <v>-53.23840110665137</v>
+        <v>1.33487258636382</v>
       </c>
       <c r="E7">
-        <v>-55.59266721589984</v>
+        <v>1.894546052252768</v>
       </c>
       <c r="F7">
-        <v>4.390514382090063</v>
+        <v>1.505530763105608</v>
       </c>
       <c r="G7">
-        <v>-56.62306739616567</v>
+        <v>-1.143462461900912</v>
       </c>
       <c r="H7">
-        <v>-46.50877909350755</v>
+        <v>2.605762487767027</v>
       </c>
       <c r="I7">
-        <v>10.11428830265812</v>
+        <v>3.749224949667938</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
@@ -774,28 +774,28 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>-2.500784269168561</v>
+        <v>-53.87625990793708</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8">
-        <v>-2.962365486903869</v>
+        <v>-53.23840110665137</v>
       </c>
       <c r="E8">
-        <v>-2.070518893146442</v>
+        <v>-55.59266721589984</v>
       </c>
       <c r="F8">
-        <v>2.494497553471604</v>
+        <v>4.390514382090063</v>
       </c>
       <c r="G8">
-        <v>-6.543068817687839</v>
+        <v>-56.62306739616567</v>
       </c>
       <c r="H8">
-        <v>-0.4870129870129816</v>
+        <v>-46.50877909350755</v>
       </c>
       <c r="I8">
-        <v>6.056055830674858</v>
+        <v>10.11428830265812</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -818,34 +818,34 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>12.876553924134</v>
+        <v>-3.244366932976385</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>11.82646376574064</v>
+        <v>-3.743499169062268</v>
       </c>
       <c r="E9">
-        <v>12.107694308957</v>
+        <v>-2.963354149741118</v>
       </c>
       <c r="F9">
-        <v>1.905061701066394</v>
+        <v>2.358553572528861</v>
       </c>
       <c r="G9">
-        <v>9.156939040207519</v>
+        <v>-7.179077005630766</v>
       </c>
       <c r="H9">
-        <v>14.43379052856994</v>
+        <v>-1.440922186651328</v>
       </c>
       <c r="I9">
-        <v>5.276851488362418</v>
+        <v>5.738154818979438</v>
       </c>
       <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>5</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -862,34 +862,34 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>-3.399779170644565</v>
+        <v>12.78893971379229</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10">
-        <v>-4.111525374436573</v>
+        <v>11.78477180888216</v>
       </c>
       <c r="E10">
-        <v>-3.602599519005729</v>
+        <v>12.08567593496913</v>
       </c>
       <c r="F10">
-        <v>1.796311822910402</v>
+        <v>1.789551454452119</v>
       </c>
       <c r="G10">
-        <v>-6.983595800042814</v>
+        <v>9.290187891440489</v>
       </c>
       <c r="H10">
-        <v>-2.606691039635062</v>
+        <v>14.24665463795645</v>
       </c>
       <c r="I10">
-        <v>4.376904760407752</v>
+        <v>4.956466746515957</v>
       </c>
       <c r="J10">
+        <v>5</v>
+      </c>
+      <c r="K10">
         <v>0</v>
-      </c>
-      <c r="K10">
-        <v>5</v>
       </c>
       <c r="L10">
         <v>100</v>

--- a/outputs/Block5B_Senate_2026_Race_Stability.xlsx
+++ b/outputs/Block5B_Senate_2026_Race_Stability.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="32">
   <si>
     <t>STATE</t>
   </si>
@@ -61,37 +61,46 @@
     <t>Kansas</t>
   </si>
   <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
     <t>Iowa</t>
   </si>
   <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
     <t>Ohio</t>
   </si>
   <si>
-    <t>Texas</t>
-  </si>
-  <si>
-    <t>Maine</t>
-  </si>
-  <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
-    <t>Nebraska</t>
+    <t>Florida</t>
   </si>
   <si>
     <t>Georgia</t>
   </si>
   <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
     <t>North Carolina</t>
-  </si>
-  <si>
-    <t>Michigan</t>
-  </si>
-  <si>
-    <t>New Hampshire</t>
   </si>
   <si>
     <t>R</t>
@@ -458,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -510,28 +519,28 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>-1.668982094438827</v>
+        <v>-1.865788738970709</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>-2.082159330100257</v>
+        <v>-2.22692356381475</v>
       </c>
       <c r="E2">
-        <v>-1.153267653173353</v>
+        <v>-1.270485350847637</v>
       </c>
       <c r="F2">
-        <v>2.551679662651943</v>
+        <v>2.616558422604596</v>
       </c>
       <c r="G2">
-        <v>-5.680203385192162</v>
+        <v>-5.880209986038962</v>
       </c>
       <c r="H2">
-        <v>0.5161640858462349</v>
+        <v>0.4907306434024008</v>
       </c>
       <c r="I2">
-        <v>6.196367471038397</v>
+        <v>6.370940629441363</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -546,7 +555,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -554,34 +563,34 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>-1.992304939694847</v>
+        <v>1.562619463970164</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>-2.434965244096224</v>
+        <v>0.985932646535238</v>
       </c>
       <c r="E3">
-        <v>-1.494981145138496</v>
+        <v>1.627971341250459</v>
       </c>
       <c r="F3">
-        <v>2.545132579532559</v>
+        <v>1.732694710942856</v>
       </c>
       <c r="G3">
-        <v>-6.063399526031018</v>
+        <v>-1.717828340340283</v>
       </c>
       <c r="H3">
-        <v>0.1082837033026536</v>
+        <v>2.427440633245382</v>
       </c>
       <c r="I3">
-        <v>6.171683229333672</v>
+        <v>4.145268973585665</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>80</v>
@@ -590,7 +599,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -598,28 +607,28 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>2.361497500491866</v>
+        <v>1.402597153343956</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>2.039296644553422</v>
+        <v>0.673980101935528</v>
       </c>
       <c r="E4">
-        <v>2.726879376671175</v>
+        <v>1.270342024125088</v>
       </c>
       <c r="F4">
-        <v>2.126226822090575</v>
+        <v>1.540016523686267</v>
       </c>
       <c r="G4">
-        <v>-0.8514681264693413</v>
+        <v>-1.881716478465326</v>
       </c>
       <c r="H4">
-        <v>4.35020519835841</v>
+        <v>1.964320154153819</v>
       </c>
       <c r="I4">
-        <v>5.201673324827751</v>
+        <v>3.846036632619145</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -634,7 +643,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -642,28 +651,28 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>1.615349717881234</v>
+        <v>1.907174422807667</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>1.001518801299071</v>
+        <v>1.144710106180717</v>
       </c>
       <c r="E5">
-        <v>1.631399086505698</v>
+        <v>1.69400909621784</v>
       </c>
       <c r="F5">
-        <v>1.721319065125029</v>
+        <v>1.432191250622833</v>
       </c>
       <c r="G5">
-        <v>-1.693838513232154</v>
+        <v>-1.268718015257621</v>
       </c>
       <c r="H5">
-        <v>2.397891963109359</v>
+        <v>2.380154888649418</v>
       </c>
       <c r="I5">
-        <v>4.091730476341513</v>
+        <v>3.648872903907039</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -678,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -686,43 +695,43 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>1.784559241874853</v>
+        <v>-53.62885373589857</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>1.05646767722283</v>
+        <v>-52.99081764994875</v>
       </c>
       <c r="E6">
-        <v>1.63222527052263</v>
+        <v>-55.34545963085596</v>
       </c>
       <c r="F6">
-        <v>1.534599067282088</v>
+        <v>4.314005711929146</v>
       </c>
       <c r="G6">
-        <v>-1.468962141794489</v>
+        <v>-56.27891424570422</v>
       </c>
       <c r="H6">
-        <v>2.350626952871099</v>
+        <v>-46.36916835699796</v>
       </c>
       <c r="I6">
-        <v>3.819589094665589</v>
+        <v>9.909745888706261</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -730,43 +739,43 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>2.056327975391802</v>
+        <v>-3.7076161482561</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>1.33487258636382</v>
+        <v>-4.060836988049704</v>
       </c>
       <c r="E7">
-        <v>1.894546052252768</v>
+        <v>-3.167965518428194</v>
       </c>
       <c r="F7">
-        <v>1.505530763105608</v>
+        <v>2.673199572677819</v>
       </c>
       <c r="G7">
-        <v>-1.143462461900912</v>
+        <v>-7.771144457473818</v>
       </c>
       <c r="H7">
-        <v>2.605762487767027</v>
+        <v>-1.235245676640133</v>
       </c>
       <c r="I7">
-        <v>3.749224949667938</v>
+        <v>6.535898780833684</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -774,28 +783,28 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>-53.87625990793708</v>
+        <v>-2.565275447343367</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D8">
-        <v>-53.23840110665137</v>
+        <v>-2.964145230592041</v>
       </c>
       <c r="E8">
-        <v>-55.59266721589984</v>
+        <v>-2.0247623622764</v>
       </c>
       <c r="F8">
-        <v>4.390514382090063</v>
+        <v>2.588488325901461</v>
       </c>
       <c r="G8">
-        <v>-56.62306739616567</v>
+        <v>-6.628330995289902</v>
       </c>
       <c r="H8">
-        <v>-46.50877909350755</v>
+        <v>-0.326086956521749</v>
       </c>
       <c r="I8">
-        <v>10.11428830265812</v>
+        <v>6.302244038768153</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -810,7 +819,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -818,28 +827,28 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>-3.244366932976385</v>
+        <v>-3.320336284398673</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D9">
-        <v>-3.743499169062268</v>
+        <v>-3.836415773997824</v>
       </c>
       <c r="E9">
-        <v>-2.963354149741118</v>
+        <v>-3.106185546449092</v>
       </c>
       <c r="F9">
-        <v>2.358553572528861</v>
+        <v>2.22877398601689</v>
       </c>
       <c r="G9">
-        <v>-7.179077005630766</v>
+        <v>-7.147327230489436</v>
       </c>
       <c r="H9">
-        <v>-1.440922186651328</v>
+        <v>-1.72043010752688</v>
       </c>
       <c r="I9">
-        <v>5.738154818979438</v>
+        <v>5.426897122962556</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -854,7 +863,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -862,28 +871,28 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>12.78893971379229</v>
+        <v>3.038156054300348</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D10">
-        <v>11.78477180888216</v>
+        <v>2.713248074965313</v>
       </c>
       <c r="E10">
-        <v>12.08567593496913</v>
+        <v>3.348339205636394</v>
       </c>
       <c r="F10">
-        <v>1.789551454452119</v>
+        <v>1.957664135694627</v>
       </c>
       <c r="G10">
-        <v>9.290187891440489</v>
+        <v>0.008955569026754873</v>
       </c>
       <c r="H10">
-        <v>14.24665463795645</v>
+        <v>4.818949087939018</v>
       </c>
       <c r="I10">
-        <v>4.956466746515957</v>
+        <v>4.809993518912263</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -898,7 +907,7 @@
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -906,34 +915,34 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>9.543498182490687</v>
+        <v>-8.482137561877773</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D11">
-        <v>9.279074024359335</v>
+        <v>-9.073625187837994</v>
       </c>
       <c r="E11">
-        <v>9.497791515143108</v>
+        <v>-8.894539561067987</v>
       </c>
       <c r="F11">
-        <v>1.179549604622028</v>
+        <v>1.834755018637456</v>
       </c>
       <c r="G11">
-        <v>7.772537436199933</v>
+        <v>-11.85949981973358</v>
       </c>
       <c r="H11">
-        <v>10.7103825136612</v>
+        <v>-7.344940152339497</v>
       </c>
       <c r="I11">
-        <v>2.937845077461269</v>
+        <v>4.514559667394082</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>5</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -942,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -950,28 +959,28 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>4.803504661876866</v>
+        <v>11.92251184757048</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D12">
-        <v>3.912833396743513</v>
+        <v>11.00267234321976</v>
       </c>
       <c r="E12">
-        <v>3.919246691079949</v>
+        <v>11.08654647454055</v>
       </c>
       <c r="F12">
-        <v>1.180333129680543</v>
+        <v>1.575949482029674</v>
       </c>
       <c r="G12">
-        <v>2.475588634409105</v>
+        <v>8.84210526315789</v>
       </c>
       <c r="H12">
-        <v>5.171540530193047</v>
+        <v>13.21213717449071</v>
       </c>
       <c r="I12">
-        <v>2.695951895783942</v>
+        <v>4.370031911332818</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -986,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -994,28 +1003,28 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>9.138347262535573</v>
+        <v>4.004415174227741</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D13">
-        <v>8.351694851278971</v>
+        <v>3.428399317051677</v>
       </c>
       <c r="E13">
-        <v>8.100876252980063</v>
+        <v>3.6727879799666</v>
       </c>
       <c r="F13">
-        <v>1.050821149840632</v>
+        <v>1.150595510333869</v>
       </c>
       <c r="G13">
-        <v>7.173678532901825</v>
+        <v>1.502192302137329</v>
       </c>
       <c r="H13">
-        <v>9.773277512312969</v>
+        <v>4.605455518747332</v>
       </c>
       <c r="I13">
-        <v>2.599598979411144</v>
+        <v>3.103263216610003</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1030,7 +1039,139 @@
         <v>1</v>
       </c>
       <c r="N13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14">
+        <v>4.146618060330528</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14">
+        <v>3.262983864156708</v>
+      </c>
+      <c r="E14">
+        <v>3.311590976692931</v>
+      </c>
+      <c r="F14">
+        <v>1.209521566542564</v>
+      </c>
+      <c r="G14">
+        <v>1.730876500872622</v>
+      </c>
+      <c r="H14">
+        <v>4.520810184903002</v>
+      </c>
+      <c r="I14">
+        <v>2.78993368403038</v>
+      </c>
+      <c r="J14">
+        <v>5</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>100</v>
+      </c>
+      <c r="M14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15">
+        <v>9.158633743871778</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15">
+        <v>8.393554913108566</v>
+      </c>
+      <c r="E15">
+        <v>8.144108148430959</v>
+      </c>
+      <c r="F15">
+        <v>1.057099351680297</v>
+      </c>
+      <c r="G15">
+        <v>7.194826192400974</v>
+      </c>
+      <c r="H15">
+        <v>9.844770809263956</v>
+      </c>
+      <c r="I15">
+        <v>2.649944616862982</v>
+      </c>
+      <c r="J15">
+        <v>5</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
         <v>28</v>
+      </c>
+      <c r="B16">
+        <v>10.30265207632678</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>10.04646445502569</v>
+      </c>
+      <c r="E16">
+        <v>10.21113469531803</v>
+      </c>
+      <c r="F16">
+        <v>1.019842065800444</v>
+      </c>
+      <c r="G16">
+        <v>8.730091189281499</v>
+      </c>
+      <c r="H16">
+        <v>11.29866594064797</v>
+      </c>
+      <c r="I16">
+        <v>2.568574751366473</v>
+      </c>
+      <c r="J16">
+        <v>5</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>100</v>
+      </c>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
